--- a/.claude/mgmt/issue-system/reports/issues_export.xlsx
+++ b/.claude/mgmt/issue-system/reports/issues_export.xlsx
@@ -735,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1291,18 +1291,148 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr"/>
     </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ISSUE-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>申請用出力フェーズ着手前の設計確認（plan_v1.md との整合確認）</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>plan_v1.md の Ph.2〜Ph.5 設計（別スクリプト構成）が現在のアーキテクチャ（merge.py 統合・output_xlsx.py / output_geojson.py 分離構成）に合っているかを確認・整合させる。ISSUE-003（output_xlsx.py）・ISSUE-004（output_geojson.py）の前提条件であり、着手前に必ず実施する。</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>設計</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>JJ1XGO</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>HLD</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>JJ1XGO</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>plan_v1.md: .claude/mgmt/plan_v1.md</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ISSUE-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>新規サミット仮コードへの地域コード自動付与</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>現在は仮コードが ZZ/ZZ-001 形式の連番。座標から都道府県を判定し、SOTA JA のアソシエーション/リージョンコード（北海道・本州・四国・九州）を仮コードに反映できるか実装を検討する。</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>機能追加</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>merge.py</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>JJ1XGO</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>HLD</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>JJ1XGO</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>将来実装候補。フルパイプ検証・申請用出力フェーズ完了後に検討。</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="J2:J8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未対応,対応中,対応完了,解決済,却下"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"機能追加,改善,調査,設計"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"URD,SRS,HLD,LLD,COD,UT,IT,ST,OPS"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1316,7 +1446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1338,7 +1468,7 @@
         </is>
       </c>
       <c r="B2" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1348,7 +1478,7 @@
         </is>
       </c>
       <c r="B3" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -1388,7 +1518,7 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -1446,7 +1576,7 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1466,7 +1596,7 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1484,7 +1614,7 @@
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1507,76 +1637,76 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>設計</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>カテゴリ別（未解決）</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>解析エンジン</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="B25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>merge.py</t>
+          <t>解析エンジン</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>GeoJSON出力</t>
+          <t>merge.py</t>
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
+          <t>GeoJSON出力</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="B29" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>ステージ別（未解決）</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>COD</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="B31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HLD</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
@@ -1586,20 +1716,40 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="B33" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
           <t>OPS</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n">
+      <c r="B36" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1650,7 +1800,7 @@
         <v>46139</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>

--- a/.claude/mgmt/issue-system/reports/issues_export.xlsx
+++ b/.claude/mgmt/issue-system/reports/issues_export.xlsx
@@ -45,7 +45,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +70,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -119,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -133,17 +138,20 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1032,69 +1040,77 @@
       <c r="O4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>ISSUE-004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>output_geojson.py 新規作成（GeoJSON生成）</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>地理院地図での目視確認用 GeoJSON を生成するスクリプト。Summit/Peak/Col ごとに Point Feature を生成。match_status 別アイコン/色（NEW=マゼンタ, MOVED=オレンジ, ELEV_CHANGE=水色, DELETED=グレー, MATCH=スコア色）。Summit→Peak, Peak→Col の LineString も追加。</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>機能追加</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>GeoJSON出力</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>SOTA スコア別色（MATCHのみ）: 10点=赤, 8点=黄, 6点=緑, 4点=シアン, 2点=青, 1点=紫</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1117,7 +1133,7 @@
           <t>調査</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1182,7 +1198,7 @@
           <t>改善</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1247,7 +1263,7 @@
           <t>改善</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -1377,7 +1393,7 @@
           <t>機能追加</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -1446,7 +1462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1454,302 +1470,292 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B1" s="8" t="n"/>
+      <c r="B1" s="9" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>合計件数</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>未解決件数</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
-        <v>9</v>
+      <c r="B3" s="11" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>解決済件数</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>解決率</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>ステータス別</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>解決率</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>ステータス別</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>対応中</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>対応完了</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>対応完了</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>却下</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>却下</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>優先度別（未解決）</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n"/>
+      <c r="B14" s="9" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>種別別（未解決）</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>機能追加</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>改善</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>種別別（未解決）</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>機能追加</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n">
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>調査</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>設計</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>カテゴリ別（未解決）</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>解析エンジン</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>merge.py</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>改善</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n">
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>ステージ別（未解決）</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>HLD</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>調査</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="n">
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>設計</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n">
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>カテゴリ別（未解決）</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>解析エンジン</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>merge.py</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>GeoJSON出力</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>ステージ別（未解決）</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>HLD</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>COD</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n">
-        <v>2</v>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>OPS</t>
         </is>
       </c>
-      <c r="B36" s="10" t="n">
+      <c r="B35" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1796,17 +1802,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n">
+      <c r="A2" s="12" t="n">
         <v>46139</v>
       </c>
       <c r="B2" t="n">
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
